--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O10" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="R10" t="n">
-        <v>1.685820625159584</v>
+        <v>1.693166248798623</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="O11" t="n">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2317</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="O10" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="R10" t="n">
-        <v>1.693166248798623</v>
+        <v>1.689493436979103</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="O11" t="n">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>181</v>
+        <v>445</v>
       </c>
       <c r="O19" t="n">
-        <v>181</v>
+        <v>445</v>
       </c>
       <c r="R19" t="n">
-        <v>0.664778939333082</v>
+        <v>1.634401259686306</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>181</v>
+        <v>445</v>
       </c>
       <c r="O20" t="n">
-        <v>181</v>
+        <v>445</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3643,7 +3643,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN20" t="b">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN28" t="b">
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2319</v>
+        <v>2582</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O10" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R10" t="n">
-        <v>1.689493436979103</v>
+        <v>1.693166248798623</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O11" t="n">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="O19" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="R19" t="n">
-        <v>1.634401259686306</v>
+        <v>1.652765318783906</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="O20" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2582</v>
+        <v>2588</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O10" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="R10" t="n">
-        <v>1.693166248798623</v>
+        <v>1.700511872437663</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="O11" t="n">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O19" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="R19" t="n">
-        <v>1.652765318783906</v>
+        <v>1.663783754242465</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="O20" t="n">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2588</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O10" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="R10" t="n">
-        <v>1.700511872437663</v>
+        <v>1.707857496076702</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O11" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="O19" t="n">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="R19" t="n">
-        <v>1.663783754242465</v>
+        <v>1.722548743354781</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="O20" t="n">
-        <v>453</v>
+        <v>469</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2593</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="O10" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="R10" t="n">
-        <v>1.707857496076702</v>
+        <v>1.696839060618143</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="O11" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="O19" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="R19" t="n">
-        <v>1.722548743354781</v>
+        <v>1.737239990632861</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="O20" t="n">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2611</v>
+        <v>2612</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O10" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="R10" t="n">
-        <v>1.696839060618143</v>
+        <v>1.707857496076702</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="O11" t="n">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="O19" t="n">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="R19" t="n">
-        <v>1.737239990632861</v>
+        <v>1.766622485189019</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="O20" t="n">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -3633,7 +3633,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2612</v>
+        <v>2623</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -2005,13 +2005,13 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O10" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="R10" t="n">
-        <v>1.707857496076702</v>
+        <v>1.711530307896222</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -2164,10 +2164,10 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O11" t="n">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O19" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="R19" t="n">
-        <v>1.766622485189019</v>
+        <v>1.762949673369499</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="O20" t="n">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="O19" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="R19" t="n">
-        <v>1.762949673369499</v>
+        <v>1.781313732467098</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="O20" t="n">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>340</v>
       </c>
       <c r="O27" t="n">
-        <v>5</v>
+        <v>340</v>
       </c>
       <c r="R27" t="n">
-        <v>0.01836405909759895</v>
+        <v>1.248756018636729</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>5</v>
+        <v>340</v>
       </c>
       <c r="O28" t="n">
-        <v>5</v>
+        <v>340</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2623</v>
+        <v>2963</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -3392,13 +3392,13 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="O19" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="R19" t="n">
-        <v>1.781313732467098</v>
+        <v>1.777640920647578</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -3551,10 +3551,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="O20" t="n">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="O27" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="R27" t="n">
-        <v>1.248756018636729</v>
+        <v>1.296502572290486</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -4796,10 +4796,10 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="O28" t="n">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2963</v>
+        <v>2975</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -21853,13 +21853,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="O111" t="n">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="R111" t="n">
-        <v>1.781313732467098</v>
+        <v>1.818041850662296</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -22012,10 +22012,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="O112" t="n">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -25147,13 +25147,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="O128" t="n">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="R128" t="n">
-        <v>1.333230690485684</v>
+        <v>1.384650055958961</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -25306,10 +25306,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="O129" t="n">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5896</v>
+        <v>5920</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -21853,13 +21853,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O111" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="R111" t="n">
-        <v>1.818041850662296</v>
+        <v>1.821714662481816</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -22012,10 +22012,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O112" t="n">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -25147,13 +25147,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O128" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="R128" t="n">
-        <v>1.384650055958961</v>
+        <v>1.391995679598</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -25306,10 +25306,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O129" t="n">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5920</v>
+        <v>5923</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -21853,13 +21853,13 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O111" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="R111" t="n">
-        <v>1.821714662481816</v>
+        <v>1.829060286120855</v>
       </c>
       <c r="S111" t="inlineStr">
         <is>
@@ -22012,10 +22012,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="O112" t="n">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
@@ -25147,13 +25147,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="O128" t="n">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="R128" t="n">
-        <v>1.391995679598</v>
+        <v>1.443415045071277</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -25306,10 +25306,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="O129" t="n">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5923</v>
+        <v>5939</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1394,7 +1394,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4052,7 +4052,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -4838,7 +4838,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7496,7 +7496,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8282,7 +8282,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8675,7 +8675,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10640,7 +10640,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11033,7 +11033,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -11819,7 +11819,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -13934,7 +13934,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -14327,7 +14327,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14720,7 +14720,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -15113,7 +15113,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -15506,7 +15506,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -16292,7 +16292,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -16685,7 +16685,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -17078,7 +17078,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -17471,7 +17471,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -18407,7 +18407,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19193,7 +19193,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -19586,7 +19586,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -19979,7 +19979,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20372,7 +20372,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -20765,7 +20765,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21308,7 +21308,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -21701,7 +21701,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -22094,7 +22094,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -22487,7 +22487,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -22880,7 +22880,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -23273,7 +23273,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -23666,7 +23666,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -24602,7 +24602,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -24995,7 +24995,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -25147,13 +25147,13 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="O128" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="R128" t="n">
-        <v>1.443415045071277</v>
+        <v>1.458106292349357</v>
       </c>
       <c r="S128" t="inlineStr">
         <is>
@@ -25306,10 +25306,10 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="O129" t="n">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="U129" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -25781,7 +25781,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -26174,7 +26174,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -26567,7 +26567,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -26960,7 +26960,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -27353,7 +27353,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -27746,7 +27746,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -28139,7 +28139,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -28532,7 +28532,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -28795,7 +28795,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5939</v>
+        <v>5943</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -10336,13 +10336,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="O69" t="n">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="R69" t="n">
-        <v>1.483815975085995</v>
+        <v>1.527889716920233</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5950</v>
+        <v>5962</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -10336,13 +10336,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="O69" t="n">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="R69" t="n">
-        <v>1.527889716920233</v>
+        <v>1.538908152378792</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5962</v>
+        <v>5965</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -10336,13 +10336,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="O69" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="R69" t="n">
-        <v>1.538908152378792</v>
+        <v>1.542580964198312</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5965</v>
+        <v>5966</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -9049,13 +9049,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O60" t="n">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="R60" t="n">
-        <v>1.829060286120855</v>
+        <v>1.832733097940375</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -11560,6 +11560,150 @@
         </is>
       </c>
       <c r="BC77" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>D232</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>infectious-syphilis-under-two-years-duration</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Infectious syphilis under two years duration</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>D232</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Infectious syphilis under two years duration</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>病程不足两年的感染性梅毒</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N78" t="n">
+        <v>264</v>
+      </c>
+      <c r="O78" t="n">
+        <v>264</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.9696223203532246</v>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_INFECTIOUS_LT2Y</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP78" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS78" t="inlineStr">
+        <is>
+          <t>SER_AU_SYPHILIS_INFECTIOUS_LT2Y</t>
+        </is>
+      </c>
+      <c r="AT78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA78" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB78" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC78" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -11598,7 +11742,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -11681,7 +11825,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -11691,7 +11835,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -11743,7 +11887,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5966</v>
+        <v>6231</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d232/2026-2029.xlsx
+++ b/diseases/d232/2026-2029.xlsx
@@ -9049,13 +9049,13 @@
         </is>
       </c>
       <c r="N60" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="O60" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="R60" t="n">
-        <v>1.832733097940375</v>
+        <v>1.836405909759895</v>
       </c>
       <c r="U60" t="inlineStr">
         <is>
@@ -10336,13 +10336,13 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="O69" t="n">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="R69" t="n">
-        <v>1.542580964198312</v>
+        <v>1.553599399656871</v>
       </c>
       <c r="U69" t="inlineStr">
         <is>
@@ -11887,7 +11887,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6231</v>
+        <v>6235</v>
       </c>
     </row>
     <row r="16">
